--- a/CBT_2023_4회/산업안전기사_2023_4회_문항등록.xlsx
+++ b/CBT_2023_4회/산업안전기사_2023_4회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
-          <t>다음 중 인간의 행동특성에 관한 레빈(Lewin)의 법칙 「B=f(PㆍE)」 에서 P에 해당되는 것은?</t>
+          <t>다음 중 인간의 행동특성에 관한 레빈(Lewin)의 법칙 「B=f(PㆍE)」에서 P에 해당되는 것은?</t>
         </is>
       </c>
       <c r="V9" s="32" t="inlineStr"/>
@@ -2233,17 +2233,17 @@
       </c>
       <c r="AG9" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;P 는 Person&lt;/strong&gt; — &lt;strong&gt;소질(개체)&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;레빈의 법칙 $B = f ( P \cdot E )$&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Behavior&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;인간의 행동&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;f&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;function&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;함수 — 두 가지가 어우러진다는 뜻&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;P&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Person&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;소질(개체) — 나이 · 성격 · 지능 · 경험 · 심신 상태&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Environment&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;환경 — 인간관계 · 작업조건 · 설비&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;P는 Person&lt;/strong&gt; — &lt;strong&gt;소질(개체)&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;레빈의 법칙 $B = f ( P \cdot E )$&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Behavior&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;인간의 행동&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;f&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;function&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;함수 — 두 가지가 어우러진다는 뜻&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;P&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Person&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;소질(개체) — 나이 · 성격 · 지능 · 경험 · 심신 상태&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Environment&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;환경 — 인간관계 · 작업조건 · 설비&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH9" s="32" t="inlineStr">
         <is>
-          <t>① 행동은 B 다.&lt;br&gt;③ 환경은 E 다.&lt;br&gt;④ 함수는 f 다.</t>
+          <t>① 행동은 B다.&lt;br&gt;③ 환경은 E다.&lt;br&gt;④ 함수는 f다.</t>
         </is>
       </c>
       <c r="AI9" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;레빈의 법칙&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;사람의 행동은 「그 사람」과 「그 자리」가 함께 만든다&lt;/strong&gt;는 뜻이다 — &lt;strong&gt;안전관리가 사람 교육과 환경 개선 양쪽을 하는&lt;/strong&gt; 까닭이 여기 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;P 는 소질, E 는 환경&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;레빈의 법칙&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;사람의 행동은 「그 사람」과 「그 자리」가 함께 만든다&lt;/strong&gt;는 뜻이다 — &lt;strong&gt;안전관리가 사람 교육과 환경 개선 양쪽을 하는&lt;/strong&gt; 까닭이 여기 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;P는 소질, E는 환경&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2878,17 +2878,17 @@
       </c>
       <c r="AG14" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;JIT(작업지도기법)&lt;/strong&gt;이다. &lt;strong&gt;가르치는 기술&lt;/strong&gt;을 다룬다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;TWI 의 네 가지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JIT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Instruction Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업지도기법 — 가르치는 기술&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JMT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Method Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업개선기법 — 일하는 방법을 고치는 기술&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JRT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Relation Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인간관계기법 — 사람을 다루는 기술&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JST&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Safety Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전작업기법 — 안전하게 일하는 기술&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;JIT(작업지도기법)&lt;/strong&gt;이다. &lt;strong&gt;가르치는 기술&lt;/strong&gt;을 다룬다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;TWI의 네 가지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JIT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Instruction Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업지도기법 — 가르치는 기술&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JMT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Method Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업개선기법 — 일하는 방법을 고치는 기술&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JRT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Relation Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인간관계기법 — 사람을 다루는 기술&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JST&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Job Safety Training&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전작업기법 — 안전하게 일하는 기술&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH14" s="32" t="inlineStr">
         <is>
-          <t>② JMT 는 작업개선기법이다.&lt;br&gt;③ JRT 는 인간관계기법이다.&lt;br&gt;④ JST 는 안전작업기법이다.</t>
+          <t>② JMT는 작업개선기법이다.&lt;br&gt;③ JRT는 인간관계기법이다.&lt;br&gt;④ JST는 안전작업기법이다.</t>
         </is>
       </c>
       <c r="AI14" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;TWI(관리감독자 훈련)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;TWI 는 관리감독자를 위한 10시간 교육&lt;/strong&gt;이다. &lt;strong&gt;Instruction(지도) · Method(방법) · Relation(관계) · Safety(안전)&lt;/strong&gt;라는 낱말이 곧 내용이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가르치는 기술은 JIT&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;TWI(관리감독자 훈련)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;TWI는 관리감독자를 위한 10시간 교육&lt;/strong&gt;이다. &lt;strong&gt;Instruction(지도) · Method(방법) · Relation(관계) · Safety(안전)&lt;/strong&gt;라는 낱말이 곧 내용이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가르치는 기술은 JIT&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3265,17 +3265,17 @@
       </c>
       <c r="AG17" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;여럿을 한꺼번에 조직적으로 훈련&lt;/strong&gt; 하는 것은 &lt;strong&gt;Off JT&lt;/strong&gt;의 장점이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;OJT 와 Off JT&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;OJT&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off JT&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;어디서&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일하는 자리에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;따로 자리를 마련해&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직속상사가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전문 강사가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;몇 명&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;한 사람 또는 소수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여럿을 한꺼번에&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;현장 실정에 맞다 · 업무의 지속성이 유지된다 · 곧바로 되먹임&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조직적 · 체계적 · 전문가에게 배운다 · 여러 매체&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;여럿을 한꺼번에 조직적으로 훈련&lt;/strong&gt;하는 것은 &lt;strong&gt;Off JT&lt;/strong&gt;의 장점이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;OJT와 Off JT&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;OJT&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off JT&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;어디서&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일하는 자리에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;따로 자리를 마련해&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직속상사가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전문 강사가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;몇 명&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;한 사람 또는 소수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여럿을 한꺼번에&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;현장 실정에 맞다 · 업무의 지속성이 유지된다 · 곧바로 되먹임&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조직적 · 체계적 · 전문가에게 배운다 · 여러 매체&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH17" s="32" t="inlineStr">
         <is>
-          <t>② 직장의 실정에 맞는 실제적 훈련은 OJT 의 장점이다.&lt;br&gt;③ 업무의 지속성이 유지되는 것도 그렇다.&lt;br&gt;④ 직속상사가 교육하는 것도 그렇다.</t>
+          <t>② 직장의 실정에 맞는 실제적 훈련은 OJT의 장점이다.&lt;br&gt;③ 업무의 지속성이 유지되는 것도 그렇다.&lt;br&gt;④ 직속상사가 교육하는 것도 그렇다.</t>
         </is>
       </c>
       <c r="AI17" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;OJT 와 Off JT&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;OJT 는 「일하면서」이므로 사람 수가 적고 현장에 딱 맞는다&lt;/strong&gt;. &lt;strong&gt;「다수」 · 「조직적」 · 「체계적」 · 「전문 강사」라는 낱말이 나오면 Off JT&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;다수·조직적이면 Off JT&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;OJT와 Off JT&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;OJT는 「일하면서」이므로 사람 수가 적고 현장에 딱 맞는다&lt;/strong&gt;. &lt;strong&gt;「다수」 · 「조직적」 · 「체계적」 · 「전문 강사」라는 낱말이 나오면 Off JT&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;다수·조직적이면 Off JT&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="AH19" s="32" t="inlineStr">
         <is>
-          <t>① 듀이의 사고과정은 시사·지식화·가설·추론·검토 다섯이다.&lt;br&gt;② 태도 교육 단계이론은 청취·이해·모범·평가와 권장이다.&lt;br&gt;④ MTP 는 관리자 훈련 프로그램이다.</t>
+          <t>① 듀이의 사고과정은 시사·지식화·가설·추론·검토 다섯이다.&lt;br&gt;② 태도 교육 단계이론은 청취·이해·모범·평가와 권장이다.&lt;br&gt;④ MTP는 관리자 훈련 프로그램이다.</t>
         </is>
       </c>
       <c r="AI19" s="32" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="U20" s="32" t="inlineStr">
         <is>
-          <t>다음 중 하인리히의 재해 손실비용 산정에 있어서 1 : 4 의 비율은 각각 무엇을 의미하는가?</t>
+          <t>다음 중 하인리히의 재해 손실비용 산정에 있어서 1 : 4의 비율은 각각 무엇을 의미하는가?</t>
         </is>
       </c>
       <c r="V20" s="32" t="inlineStr"/>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="AG21" s="32" t="inlineStr">
         <is>
-          <t>연근로시간은 224,000시간이다. 도수율 $\dfrac{5}{224 {,} 000} \times 10^{6} = 22.32$, 근로손실일수 $7 {,} 500 + 180 \times \dfrac{280}{365} = 7 {,} 638$ 이므로 강도율 $34.10$ 이다. $\mathrm{FSI} = \sqrt{22.32 \times 34.10} \fallingdotseq 27.59$ 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;종합재해지수(FSI)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연근로시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100 × 8 × 280 = 224,000&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;도수율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{5}{224 {,} 000} \times 10^{6} = 22.32$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;재해건수 5건&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;근로손실일수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사망 7,500 + 180 × 280/365 = 7,638&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사망 1명은 7,500일&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{7 {,} 638}{224 {,} 000} \times 10^{3} = 34.10$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;종합재해지수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\sqrt{\text{도수율} \times \text{강도율}} = 27.59$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기하평균&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>연근로시간은 224,000시간이다. 도수율 $\dfrac{5}{224 {,} 000} \times 10^{6} = 22.32$, 근로손실일수 $7 {,} 500 + 180 \times \dfrac{280}{365} = 7 {,} 638$이므로 강도율 $34.10$이다. $\mathrm{FSI} = \sqrt{22.32 \times 34.10} \fallingdotseq 27.59$다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;종합재해지수(FSI)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연근로시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100 × 8 × 280 = 224,000&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;도수율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{5}{224 {,} 000} \times 10^{6} = 22.32$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;재해건수 5건&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;근로손실일수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사망 7,500 + 180 × 280/365 = 7,638&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사망 1명은 7,500일&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{7 {,} 638}{224 {,} 000} \times 10^{3} = 34.10$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;종합재해지수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\sqrt{\text{도수율} \times \text{강도율}} = 27.59$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기하평균&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH21" s="32" t="inlineStr">
         <is>
-          <t>① 22.32 는 도수율이다.&lt;br&gt;③ 34.14 는 강도율에 가까운 값이다.&lt;br&gt;④ 56.42 는 두 값을 더한 값에 가깝다.</t>
+          <t>① 22.32는 도수율이다.&lt;br&gt;③ 34.14는 강도율에 가까운 값이다.&lt;br&gt;④ 56.42는 두 값을 더한 값에 가깝다.</t>
         </is>
       </c>
       <c r="AI21" s="32" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="AG25" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;우선적 AND 게이트&lt;/strong&gt;다. &lt;strong&gt;정해진 차례대로 일어나야만&lt;/strong&gt; 출력이 난다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 의 특수 논리게이트&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;게이트&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;우선적 AND&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정해진 순서대로 일어날 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;조합 AND&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력 n 개 중 m 개가 일어날 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2 out of 3 등&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;배타적 OR&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력 가운데 하나만 일어날 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;동시에 일어나면 출력 없음&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;억제 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조건이 만족될 때만 입력이 출력으로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;조건은 육각형으로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험지속 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력이 일정 시간 이어질 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;우선적 AND 게이트&lt;/strong&gt;다. &lt;strong&gt;정해진 차례대로 일어나야만&lt;/strong&gt; 출력이 난다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA의 특수 논리게이트&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;게이트&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;우선적 AND&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정해진 순서대로 일어날 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;조합 AND&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력 n 개 중 m 개가 일어날 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2 out of 3 등&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;배타적 OR&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력 가운데 하나만 일어날 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;동시에 일어나면 출력 없음&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;억제 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조건이 만족될 때만 입력이 출력으로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;조건은 육각형으로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험지속 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력이 일정 시간 이어질 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH25" s="32" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="AI25" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 의 논리게이트&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「순서」라는 낱말이 곧 우선적 AND&lt;/strong&gt;를 가리킨다. &lt;strong&gt;보통의 AND 는 순서를 따지지 않고 모두 일어나기만 하면&lt;/strong&gt; 된다는 점이 다르다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;순서가 있으면 우선적 AND&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA의 논리게이트&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「순서」라는 낱말이 곧 우선적 AND&lt;/strong&gt;를 가리킨다. &lt;strong&gt;보통의 AND는 순서를 따지지 않고 모두 일어나기만 하면&lt;/strong&gt; 된다는 점이 다르다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;순서가 있으면 우선적 AND&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AH26" s="32" t="inlineStr">
         <is>
-          <t>① 현실 상황에 맞는 조명수준으로 잡는 것은 맞다.&lt;br&gt;② 표적 탐지 활동을 50 ~ 99% 로 잡는 것도 맞다.&lt;br&gt;③ 정적인 과녁에서 동적인 과녁으로 하는 것도 맞다.</t>
+          <t>① 현실 상황에 맞는 조명수준으로 잡는 것은 맞다.&lt;br&gt;② 표적 탐지 활동을 50 ~ 99%로 잡는 것도 맞다.&lt;br&gt;③ 정적인 과녁에서 동적인 과녁으로 하는 것도 맞다.</t>
         </is>
       </c>
       <c r="AI26" s="32" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AH29" s="32" t="inlineStr">
         <is>
-          <t>① bt 는 인간 신뢰도의 단위가 아니다.&lt;br&gt;③ λ(t) 는 시간에 따라 이어지는 직무의 오류율이다.&lt;br&gt;④ α(t) 도 기본단위가 아니다.</t>
+          <t>① bt는 인간 신뢰도의 단위가 아니다.&lt;br&gt;③ λ(t)는 시간에 따라 이어지는 직무의 오류율이다.&lt;br&gt;④ α(t) 도 기본단위가 아니다.</t>
         </is>
       </c>
       <c r="AI29" s="32" t="inlineStr">
@@ -4918,12 +4918,12 @@
       </c>
       <c r="AG30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;THERP&lt;/strong&gt;다. &lt;strong&gt;사람의 오류 확률을 셈해&lt;/strong&gt; 인간공학적 대책을 세운다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주요 분석기법&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기법&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;THERP&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인간 오류율을 예측한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사건나무로 인간의 행동을 갈래지어 확률을 매긴다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;CA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;치명도 분석&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;고장의 심각성을 등급으로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;FMEA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;부품의 고장 형태와 영향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;기계 쪽 · 정성적&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;MORT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관리·운영상의 결함을 FTA 로 파고든다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;원자력 분야&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;THERP&lt;/strong&gt;다. &lt;strong&gt;사람의 오류 확률을 셈해&lt;/strong&gt; 인간공학적 대책을 세운다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주요 분석기법&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기법&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;THERP&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인간 오류율을 예측한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사건나무로 인간의 행동을 갈래지어 확률을 매긴다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;CA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;치명도 분석&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;고장의 심각성을 등급으로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;FMEA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;부품의 고장 형태와 영향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;기계 쪽 · 정성적&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;MORT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관리·운영상의 결함을 FTA로 파고든다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;원자력 분야&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH30" s="32" t="inlineStr">
         <is>
-          <t>① CA 는 치명도 분석이다.&lt;br&gt;② FMEA 는 부품의 고장 형태와 영향을 보는 기법이다.&lt;br&gt;④ MORT 는 관리·운영상의 결함을 FTA 로 파고드는 기법이다.</t>
+          <t>① CA는 치명도 분석이다.&lt;br&gt;② FMEA는 부품의 고장 형태와 영향을 보는 기법이다.&lt;br&gt;④ MORT는 관리·운영상의 결함을 FTA로 파고드는 기법이다.</t>
         </is>
       </c>
       <c r="AI30" s="32" t="inlineStr">
@@ -5047,12 +5047,12 @@
       </c>
       <c r="AG31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;교육훈련을 시작하는 것&lt;/strong&gt;은 &lt;strong&gt;생산단계&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;시스템 수명주기 5단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;구상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시스템 안전성에 관한 기본 방침&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;PHA&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정의&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전성 있는 시스템으로 구체화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;SSHA&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;개발&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설계의 수용가능성 검토 · FMEA · OHA 의 입력자료&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;생산&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;교육훈련 시작 · 품질관리 · 안전점검&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「교육훈련」은 여기&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;운전(배치)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;운영·유지보수 · 사고조사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;교육훈련을 시작하는 것&lt;/strong&gt;은 &lt;strong&gt;생산단계&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;시스템 수명주기 5단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;구상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시스템 안전성에 관한 기본 방침&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;PHA&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정의&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전성 있는 시스템으로 구체화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;SSHA&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;개발&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설계의 수용가능성 검토 · FMEA · OHA의 입력자료&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;생산&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;교육훈련 시작 · 품질관리 · 안전점검&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「교육훈련」은 여기&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;운전(배치)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;운영·유지보수 · 사고조사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH31" s="32" t="inlineStr">
         <is>
-          <t>② 위험분석으로 FMEA 를 적용하는 것은 개발단계다.&lt;br&gt;③ 설계의 수용가능성을 검토하는 것도 그렇다.&lt;br&gt;④ 모형분석과 검사결과가 OHA 의 입력자료가 되는 것도 그렇다.</t>
+          <t>② 위험분석으로 FMEA를 적용하는 것은 개발단계다.&lt;br&gt;③ 설계의 수용가능성을 검토하는 것도 그렇다.&lt;br&gt;④ 모형분석과 검사결과가 OHA의 입력자료가 되는 것도 그렇다.</t>
         </is>
       </c>
       <c r="AI31" s="32" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="AI32" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;평균 고장간격(MTBF)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「고장 사이의 시간」이므로 고쳐 세워 둔 18시간은 빼야&lt;/strong&gt; 한다. &lt;strong&gt;120 을 그대로 9로 나누면 13.33 이 나와 보기에 없는&lt;/strong&gt; 값이 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;MTBF = 가동시간 ÷ 고장 횟수&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;평균 고장간격(MTBF)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「고장 사이의 시간」이므로 고쳐 세워 둔 18시간은 빼야&lt;/strong&gt; 한다. &lt;strong&gt;120을 그대로 9로 나누면 13.33이 나와 보기에 없는&lt;/strong&gt; 값이 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;MTBF = 가동시간 ÷ 고장 횟수&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="AI36" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;음원 방향의 지각&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;귀가 둘이라서 방향을 안다&lt;/strong&gt; — &lt;strong&gt;두 귀에 닿는 「세기」와 「때」의 차이&lt;/strong&gt;가 전부다. &lt;strong&gt;정면과 정후면은 두 차이가 모두 0 이라 헷갈린다&lt;/strong&gt;는 것도 여기서 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;강도차와 위상차&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;음원 방향의 지각&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;귀가 둘이라서 방향을 안다&lt;/strong&gt; — &lt;strong&gt;두 귀에 닿는 「세기」와 「때」의 차이&lt;/strong&gt;가 전부다. &lt;strong&gt;정면과 정후면은 두 차이가 모두 0이라 헷갈린다&lt;/strong&gt;는 것도 여기서 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;강도차와 위상차&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       <c r="Y37" s="32" t="inlineStr"/>
       <c r="Z37" s="32" t="inlineStr">
         <is>
-          <t>「X」가 조종장치의 변위량, 「Y」가 표시장치의 변위량일 때 X/Y 로 표현된다.</t>
+          <t>「X」가 조종장치의 변위량, 「Y」가 표시장치의 변위량일 때 X/Y로 표현된다.</t>
         </is>
       </c>
       <c r="AA37" s="32" t="inlineStr"/>
@@ -5821,17 +5821,17 @@
       </c>
       <c r="AG37" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;C/R비가 클수록 둔감&lt;/strong&gt; 하다. &lt;strong&gt;많이 돌려야 조금 움직이기&lt;/strong&gt; 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;조종-반응비율(C/R비)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$C / R = \dfrac{\text{조종장치의 변위량}}{\text{표시장치의 변위량}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;C/R비가 크면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;많이 돌려야 조금 움직인다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;둔감&lt;/u&gt; · 미세조종 시간이 짧다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;C/R비가 작으면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조금만 돌려도 크게 움직인다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;민감&lt;/u&gt; · 이동시간이 짧다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최적값&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이동시간과 미세조종시간의 합이 가장 작은 곳&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;장치 종류·표시장치 크기·허용오차에 따라 달라진다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;C/R비가 클수록 둔감&lt;/strong&gt;하다. &lt;strong&gt;많이 돌려야 조금 움직이기&lt;/strong&gt; 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;조종-반응비율(C/R비)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$C / R = \dfrac{\text{조종장치의 변위량}}{\text{표시장치의 변위량}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;C/R비가 크면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;많이 돌려야 조금 움직인다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;둔감&lt;/u&gt; · 미세조종 시간이 짧다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;C/R비가 작으면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조금만 돌려도 크게 움직인다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;민감&lt;/u&gt; · 이동시간이 짧다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최적값&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이동시간과 미세조종시간의 합이 가장 작은 곳&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;장치 종류·표시장치 크기·허용오차에 따라 달라진다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH37" s="32" t="inlineStr">
         <is>
-          <t>② X/Y 로 표현되는 것은 맞다.&lt;br&gt;③ Knob C/R비를 1회전 시 표시장치 이동거리의 역수로 나타내는 것도 맞다.&lt;br&gt;④ 최적 C/R비가 장치 종류와 표시장치 크기, 허용오차에 따라 달라지는 것도 맞다.</t>
+          <t>② X/Y로 표현되는 것은 맞다.&lt;br&gt;③ Knob C/R비를 1회전 시 표시장치 이동거리의 역수로 나타내는 것도 맞다.&lt;br&gt;④ 최적 C/R비가 장치 종류와 표시장치 크기, 허용오차에 따라 달라지는 것도 맞다.</t>
         </is>
       </c>
       <c r="AI37" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;조종-반응비율(C/R비)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;분모가 표시장치&lt;/strong&gt;이므로 &lt;strong&gt;C/R비가 커진다는 것은 표시장치가 덜 움직인다&lt;/strong&gt;는 뜻이다 — &lt;strong&gt;곧 둔감&lt;/strong&gt; 하다. &lt;strong&gt;민감과 둔감을 뒤집어 놓는 것&lt;/strong&gt;이 이 유형의 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;C/R비가 크면 둔감&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;조종-반응비율(C/R비)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;분모가 표시장치&lt;/strong&gt;이므로 &lt;strong&gt;C/R비가 커진다는 것은 표시장치가 덜 움직인다&lt;/strong&gt;는 뜻이다 — &lt;strong&gt;곧 둔감&lt;/strong&gt;하다. &lt;strong&gt;민감과 둔감을 뒤집어 놓는 것&lt;/strong&gt;이 이 유형의 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;C/R비가 크면 둔감&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6079,17 +6079,17 @@
       </c>
       <c r="AG39" s="32" t="inlineStr">
         <is>
-          <t>15분(1/4시간)의 기준은 &lt;strong&gt;115 [dB(A)]&lt;/strong&gt;다. &lt;strong&gt;120 [dB(A)] 가 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;소음의 1일 노출기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;노출시간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;소음강도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;8시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;90 [dB(A)]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;95 [dB(A)]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100 [dB(A)]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;105 [dB(A)]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;110 [dB(A)]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;15분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;115 [dB(A)]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「120」이 아니다&lt;/u&gt; · 최대 기준&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>15분(1/4시간)의 기준은 &lt;strong&gt;115 [dB(A)]&lt;/strong&gt;다. &lt;strong&gt;120 [dB(A)]가 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;소음의 1일 노출기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;노출시간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;소음강도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;8시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;90 [dB(A)]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;95 [dB(A)]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100 [dB(A)]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;105 [dB(A)]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;110 [dB(A)]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;15분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;115 [dB(A)]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「120」이 아니다&lt;/u&gt; · 최대 기준&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH39" s="32" t="inlineStr">
         <is>
-          <t>① 8시간 90 [dB(A)] 는 맞다.&lt;br&gt;② 2시간 100 [dB(A)] 도 맞다.&lt;br&gt;③ 30분 110 [dB(A)] 도 맞다.</t>
+          <t>① 8시간 90 [dB(A)]는 맞다.&lt;br&gt;② 2시간 100 [dB(A)] 도 맞다.&lt;br&gt;③ 30분 110 [dB(A)] 도 맞다.</t>
         </is>
       </c>
       <c r="AI39" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;소음의 노출기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;90 [dB] 에서 시작해 5 [dB] 오를 때마다 시간이 절반&lt;/strong&gt;으로 준다 — &lt;strong&gt;90-8, 95-4, 100-2, 105-1, 110-1/2, 115-1/4&lt;/strong&gt;. &lt;strong&gt;115 [dB(A)] 가 끝이고 그 위로는 잠깐도 안 된다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;5 [dB] 오르면 시간은 절반&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;소음의 노출기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;90 [dB]에서 시작해 5 [dB] 오를 때마다 시간이 절반&lt;/strong&gt;으로 준다 — &lt;strong&gt;90-8, 95-4, 100-2, 105-1, 110-1/2, 115-1/4&lt;/strong&gt;. &lt;strong&gt;115 [dB(A)]가 끝이고 그 위로는 잠깐도 안 된다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;5 [dB] 오르면 시간은 절반&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="AG41" s="32" t="inlineStr">
         <is>
-          <t>조명 강도의 대수치에 &lt;strong&gt;선형적으로 「비례」&lt;/strong&gt; 한다. &lt;strong&gt;밝을수록 깜박임을 잘 가려낸다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;점멸융합주파수(CFF)에 영향을 주는 변수&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;변수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;영향&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;조명 강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대수치에 선형적으로 비례&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「반비례」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;표적과 주변의 휘도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;같을 때 최대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;색상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;휘도만 같으면 영향 없다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사람&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개인차는 크나 한 사람 안에서는 일관&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정신적 피로 · 암조응&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;내려간다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;피로의 척도&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>조명 강도의 대수치에 &lt;strong&gt;선형적으로 「비례」&lt;/strong&gt;한다. &lt;strong&gt;밝을수록 깜박임을 잘 가려낸다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;점멸융합주파수(CFF)에 영향을 주는 변수&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;변수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;영향&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;조명 강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대수치에 선형적으로 비례&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「반비례」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;표적과 주변의 휘도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;같을 때 최대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;색상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;휘도만 같으면 영향 없다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사람&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개인차는 크나 한 사람 안에서는 일관&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정신적 피로 · 암조응&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;내려간다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;피로의 척도&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH41" s="32" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="AI41" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;점멸융합주파수(CFF)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;밝고 또렷할수록 깜박임을 잘 구별&lt;/strong&gt; 하므로 CFF 가 높다. &lt;strong&gt;VFF · CFF · 플리커치는 모두 같은 값&lt;/strong&gt;을 가리키는 다른 이름이다. &lt;strong&gt;피로하거나 어두우면 내려간다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;조명 강도에 비례&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;점멸융합주파수(CFF)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;밝고 또렷할수록 깜박임을 잘 구별&lt;/strong&gt;하므로 CFF가 높다. &lt;strong&gt;VFF · CFF · 플리커치는 모두 같은 값&lt;/strong&gt;을 가리키는 다른 이름이다. &lt;strong&gt;피로하거나 어두우면 내려간다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;조명 강도에 비례&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="AH42" s="32" t="inlineStr">
         <is>
-          <t>① 2,000 [Hz] 는 회화음역이라 나중에 나빠진다.&lt;br&gt;③ 10,000 [Hz] 는 소음성 난청의 시작 대역이 아니다.&lt;br&gt;④ 20,000 [Hz] 는 가청 범위의 끝이다.</t>
+          <t>① 2,000 [Hz]는 회화음역이라 나중에 나빠진다.&lt;br&gt;③ 10,000 [Hz]는 소음성 난청의 시작 대역이 아니다.&lt;br&gt;④ 20,000 [Hz]는 가청 범위의 끝이다.</t>
         </is>
       </c>
       <c r="AI42" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;소음성 난청&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;4,000 [Hz] 부터 파이므로 초기에는 본인이 알아채지 못한다&lt;/strong&gt; — &lt;strong&gt;말소리는 500 ~ 2,000 [Hz] 라 대화에 지장이 없기&lt;/strong&gt; 때문이다. &lt;strong&gt;건강진단으로 일찍 잡아야 하는&lt;/strong&gt; 까닭이 여기 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;소음성 난청은 4,000 [Hz]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;소음성 난청&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;4,000 [Hz]부터 파이므로 초기에는 본인이 알아채지 못한다&lt;/strong&gt; — &lt;strong&gt;말소리는 500 ~ 2,000 [Hz] 라 대화에 지장이 없기&lt;/strong&gt; 때문이다. &lt;strong&gt;건강진단으로 일찍 잡아야 하는&lt;/strong&gt; 까닭이 여기 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;소음성 난청은 4,000 [Hz]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6595,17 +6595,17 @@
       </c>
       <c r="AG43" s="32" t="inlineStr">
         <is>
-          <t>$V = \dfrac{\pi D N}{1 {,} 000} = \dfrac{\pi \times 200 \times 600}{1 {,} 000} \fallingdotseq 377$ [m/min] 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;원주속도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;[m/min]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V = \dfrac{\pi D N}{1 {,} 000}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;D 는 [mm], N 은 [rpm]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;[m/s]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V = \dfrac{\pi D N}{1 {,} 000 \times 60}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;지름 20 [cm] = 200 [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;단위 환산이 갈림길&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$V = \dfrac{\pi D N}{1 {,} 000} = \dfrac{\pi \times 200 \times 600}{1 {,} 000} \fallingdotseq 377$ [m/min]이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;원주속도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;[m/min]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V = \dfrac{\pi D N}{1 {,} 000}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;D는 [mm], N은 [rpm]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;[m/s]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V = \dfrac{\pi D N}{1 {,} 000 \times 60}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;지름 20 [cm] = 200 [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;단위 환산이 갈림길&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH43" s="32" t="inlineStr">
         <is>
-          <t>① 37.7 [m/min] 은 지름을 20 [mm] 로 잘못 본 값이다.&lt;br&gt;② 251 [m/min] 은 계산과 맞지 않는다.&lt;br&gt;④ 1,200 [m/min] 도 그렇다.</t>
+          <t>① 37.7 [m/min]은 지름을 20 [mm]로 잘못 본 값이다.&lt;br&gt;② 251 [m/min]은 계산과 맞지 않는다.&lt;br&gt;④ 1,200 [m/min] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI43" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;연삭숫돌의 원주속도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;지름을 [mm] 로 바꾸는 데서 열에 아홉이 갈린다&lt;/strong&gt; — &lt;strong&gt;20 [cm] 는 200 [mm]&lt;/strong&gt;다. &lt;strong&gt;[m/s] 를 물으면 60 으로 한 번 더 나눈다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $V = \dfrac{\pi D N}{1 {,} 000}$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;연삭숫돌의 원주속도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;지름을 [mm]로 바꾸는 데서 열에 아홉이 갈린다&lt;/strong&gt; — &lt;strong&gt;20 [cm]는 200 [mm]&lt;/strong&gt;다. &lt;strong&gt;[m/s]를 물으면 60으로 한 번 더 나눈다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $V = \dfrac{\pi D N}{1 {,} 000}$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6724,12 +6724,12 @@
       </c>
       <c r="AG44" s="32" t="inlineStr">
         <is>
-          <t>$V = \dfrac{\pi \times 10 \times 1 {,} 000}{1 {,} 000} \fallingdotseq 31.4$ [m/min] 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;회전기계의 원주속도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연삭기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;숫돌의 바깥지름&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;드릴링 머신&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;드릴의 지름&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;선반&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;공작물의 지름&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;밀링&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;커터의 지름&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$V = \dfrac{\pi \times 10 \times 1 {,} 000}{1 {,} 000} \fallingdotseq 31.4$ [m/min]이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;회전기계의 원주속도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연삭기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;숫돌의 바깥지름&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;드릴링 머신&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;드릴의 지름&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;선반&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;공작물의 지름&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;밀링&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;커터의 지름&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH44" s="32" t="inlineStr">
         <is>
-          <t>① 6.28 [m/min] 은 회전수를 잘못 넣은 값이다.&lt;br&gt;③ 62.8 [m/min] 은 지름을 두 배로 본 값이다.&lt;br&gt;④ 314 [m/min] 은 자릿수가 어긋난다.</t>
+          <t>① 6.28 [m/min]은 회전수를 잘못 넣은 값이다.&lt;br&gt;③ 62.8 [m/min]은 지름을 두 배로 본 값이다.&lt;br&gt;④ 314 [m/min]은 자릿수가 어긋난다.</t>
         </is>
       </c>
       <c r="AI44" s="32" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="AG49" s="32" t="inlineStr">
         <is>
-          <t>안전블록은 &lt;strong&gt;제거가 아니라 설치&lt;/strong&gt; 한다. &lt;strong&gt;슬라이드가 제 무게로 떨어지는 것을 받쳐&lt;/strong&gt; 준다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;금형 설치·조정의 안전수칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부착 전에 하사점을 확인한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전블록을 설치한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「제거」가 아니다&lt;/u&gt; — 슬라이드의 불시하강을 막는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;올바른 치공구로 균등하게 체결한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하형부터 잡는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무거운 금형의 받침은 인력으로 하지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전원을 끄고 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>안전블록은 &lt;strong&gt;제거가 아니라 설치&lt;/strong&gt;한다. &lt;strong&gt;슬라이드가 제 무게로 떨어지는 것을 받쳐&lt;/strong&gt; 준다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;금형 설치·조정의 안전수칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부착 전에 하사점을 확인한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전블록을 설치한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「제거」가 아니다&lt;/u&gt; — 슬라이드의 불시하강을 막는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;올바른 치공구로 균등하게 체결한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하형부터 잡는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무거운 금형의 받침은 인력으로 하지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전원을 끄고 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH49" s="32" t="inlineStr">
@@ -7502,17 +7502,17 @@
       </c>
       <c r="AG50" s="32" t="inlineStr">
         <is>
-          <t>안전도는 &lt;strong&gt;인장강도 ÷ 내압&lt;/strong&gt;이다. $1 \rightarrow 40 / 50 = 0.80$, $2 \rightarrow 50 / 60 = 0.83$, $3 \rightarrow 55 / 70 = 0.79$ 이므로 &lt;strong&gt;2 - 1 - 3&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;세 용기의 안전도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;안전도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 ÷ 50 = 0.80&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;둘째&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;50 ÷ 60 = 0.83&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 높다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;55 ÷ 70 = 0.79&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 낮다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;차례&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 - 1 - 3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>안전도는 &lt;strong&gt;인장강도 ÷ 내압&lt;/strong&gt;이다. $1 \rightarrow 40 / 50 = 0.80$, $2 \rightarrow 50 / 60 = 0.83$, $3 \rightarrow 55 / 70 = 0.79$이므로 &lt;strong&gt;2 - 1 - 3&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;세 용기의 안전도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;안전도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 ÷ 50 = 0.80&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;둘째&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;50 ÷ 60 = 0.83&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 높다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;55 ÷ 70 = 0.79&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 낮다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;차례&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 - 1 - 3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH50" s="32" t="inlineStr">
         <is>
-          <t>① 1 - 2 - 3 은 계산과 맞지 않는다.&lt;br&gt;② 2 - 3 - 1 도 그렇다.&lt;br&gt;③ 3 - 1 - 2 도 그렇다.</t>
+          <t>① 1 - 2 - 3은 계산과 맞지 않는다.&lt;br&gt;② 2 - 3 - 1 도 그렇다.&lt;br&gt;③ 3 - 1 - 2 도 그렇다.</t>
         </is>
       </c>
       <c r="AI50" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전율(안전계수)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;안전도는 「버티는 힘 ÷ 걸리는 힘」&lt;/strong&gt;이다 — &lt;strong&gt;인장강도가 커도 내압이 더 크면 안전도는 낮아진다&lt;/strong&gt;. &lt;strong&gt;세 값이 0.79 ~ 0.83 으로 가까우니 반드시 나눠 봐야&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;안전도 = 인장강도 ÷ 내압&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;안전율(안전계수)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;안전도는 「버티는 힘 ÷ 걸리는 힘」&lt;/strong&gt;이다 — &lt;strong&gt;인장강도가 커도 내압이 더 크면 안전도는 낮아진다&lt;/strong&gt;. &lt;strong&gt;세 값이 0.79 ~ 0.83으로 가까우니 반드시 나눠 봐야&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;안전도 = 인장강도 ÷ 내압&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7631,12 +7631,12 @@
       </c>
       <c r="AG51" s="32" t="inlineStr">
         <is>
-          <t>$\dfrac{35}{4} = 8.75$ [kg/mm²] 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전율과 허용응력&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$S = \dfrac{\text{극한강도} ( \text{인장강도} )}{\text{허용응력}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;허용응력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{극한강도}}{\text{안전율}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전율의 다른 꼴&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{파단하중}}{\text{안전하중}}$, $\dfrac{\text{파괴하중}}{\text{최대사용하중}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$\dfrac{35}{4} = 8.75$ [kg/mm²]이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전율과 허용응력&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$S = \dfrac{\text{극한강도} ( \text{인장강도} )}{\text{허용응력}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;허용응력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{극한강도}}{\text{안전율}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전율의 다른 꼴&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{파단하중}}{\text{안전하중}}$, $\dfrac{\text{파괴하중}}{\text{최대사용하중}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH51" s="32" t="inlineStr">
         <is>
-          <t>① 7.64 는 계산과 맞지 않는다.&lt;br&gt;③ 9.87 도 그렇다.&lt;br&gt;④ 10.23 도 그렇다.</t>
+          <t>① 7.64는 계산과 맞지 않는다.&lt;br&gt;③ 9.87 도 그렇다.&lt;br&gt;④ 10.23 도 그렇다.</t>
         </is>
       </c>
       <c r="AI51" s="32" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="AH56" s="32" t="inlineStr">
         <is>
-          <t>① 98 [kPa] 는 기준값이 아니다.&lt;br&gt;③ 147 [kPa] 도 그렇다.&lt;br&gt;④ 196 [kPa] 도 그렇다.</t>
+          <t>① 98 [kPa]는 기준값이 아니다.&lt;br&gt;③ 147 [kPa] 도 그렇다.&lt;br&gt;④ 196 [kPa] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI56" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;아세틸렌 용접장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;아세틸렌은 압력이 오르면 스스로 분해 폭발&lt;/strong&gt; 한다 — &lt;strong&gt;127 [kPa] 라는 낮은 한계&lt;/strong&gt;가 그 때문이다. &lt;strong&gt;구리·은과 만나면 폭발성 화합물이 생긴다&lt;/strong&gt;는 것도 짝으로 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;아세틸렌은 127 [kPa] 이하&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;아세틸렌 용접장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;아세틸렌은 압력이 오르면 스스로 분해 폭발&lt;/strong&gt;한다 — &lt;strong&gt;127 [kPa]라는 낮은 한계&lt;/strong&gt;가 그 때문이다. &lt;strong&gt;구리·은과 만나면 폭발성 화합물이 생긴다&lt;/strong&gt;는 것도 짝으로 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;아세틸렌은 127 [kPa] 이하&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="AG58" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;재료의 종류와 물성에 크게 좌우&lt;/strong&gt; 된다. &lt;strong&gt;재료마다 소리가 다르기&lt;/strong&gt; 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;음향방출시험(AE)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;금이 자라며 내는 소리(탄성파)를 잡아낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;장점&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가동 중 검사 · 결함이 커지기 전에 알아챈다 · 결함의 위치까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단점&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;온도·분위기 등 외적 요인에 민감 · 재료의 종류와 물성에 좌우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「관계없이」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;쓰는 곳&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;압력용기 · 배관 · 저장탱크&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;재료의 종류와 물성에 크게 좌우&lt;/strong&gt;된다. &lt;strong&gt;재료마다 소리가 다르기&lt;/strong&gt; 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;음향방출시험(AE)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;금이 자라며 내는 소리(탄성파)를 잡아낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;장점&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가동 중 검사 · 결함이 커지기 전에 알아챈다 · 결함의 위치까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단점&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;온도·분위기 등 외적 요인에 민감 · 재료의 종류와 물성에 좌우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「관계없이」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;쓰는 곳&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;압력용기 · 배관 · 저장탱크&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH58" s="32" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="AG59" s="32" t="inlineStr">
         <is>
-          <t>$\dfrac{5}{20} \times 100 = 25$ [%] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차의 안정도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{안정도} = \dfrac{\text{높이} ( H )}{\text{수평거리} ( L )} \times 100$ [%]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 시 전후 안정도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4% 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;5톤 이상은 3.5% 이하&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 시 전후 안정도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;18% 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 시 좌우 안정도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6% 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 시 좌우 안정도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;(15 + 1.1V)% 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;V 는 최고속도 [km/h]&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$\dfrac{5}{20} \times 100 = 25$ [%]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차의 안정도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{안정도} = \dfrac{\text{높이} ( H )}{\text{수평거리} ( L )} \times 100$ [%]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 시 전후 안정도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4% 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;5톤 이상은 3.5% 이하&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 시 전후 안정도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;18% 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 시 좌우 안정도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6% 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 시 좌우 안정도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;(15 + 1.1V)% 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;V는 최고속도 [km/h]&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH59" s="32" t="inlineStr">
         <is>
-          <t>① 10% 는 계산과 맞지 않는다.&lt;br&gt;② 20% 도 그렇다.&lt;br&gt;④ 40% 도 그렇다.</t>
+          <t>① 10%는 계산과 맞지 않는다.&lt;br&gt;② 20% 도 그렇다.&lt;br&gt;④ 40% 도 그렇다.</t>
         </is>
       </c>
       <c r="AI59" s="32" t="inlineStr">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="AI60" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;양중기의 정격속도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「싣고 · 올라갈 때 · 최고」 세 낱말&lt;/strong&gt;이 모두 들어가야 맞다. &lt;strong&gt;올라갈 때가 가장 힘이 들고 위험&lt;/strong&gt; 하므로 그 값을 기준으로 삼는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;싣고 올라갈 때의 최고속도&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;양중기의 정격속도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「싣고 · 올라갈 때 · 최고」 세 낱말&lt;/strong&gt;이 모두 들어가야 맞다. &lt;strong&gt;올라갈 때가 가장 힘이 들고 위험&lt;/strong&gt;하므로 그 값을 기준으로 삼는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;싣고 올라갈 때의 최고속도&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9184,12 +9184,12 @@
       </c>
       <c r="AH63" s="32" t="inlineStr">
         <is>
-          <t>② 1,000 [Ω] 은 상한을 넘는다.&lt;br&gt;③ 1,500 [Ω] 도 그렇다.&lt;br&gt;④ 2,000 [Ω] 도 그렇다.</t>
+          <t>② 1,000 [Ω]은 상한을 넘는다.&lt;br&gt;③ 1,500 [Ω] 도 그렇다.&lt;br&gt;④ 2,000 [Ω] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI63" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;자동전격방지기&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;시동감도는 「몇 옴까지를 용접 시작으로 볼 것인가」&lt;/strong&gt;다 — &lt;strong&gt;사람의 몸 저항은 그보다 훨씬 크므로 500 [Ω] 을 넘겨 잡으면 사람에 닿았을 때도 전압을 올린다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;시동감도 상한은 500 [Ω]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;자동전격방지기&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;시동감도는 「몇 옴까지를 용접 시작으로 볼 것인가」&lt;/strong&gt;다 — &lt;strong&gt;사람의 몸 저항은 그보다 훨씬 크므로 500 [Ω]을 넘겨 잡으면 사람에 닿았을 때도 전압을 올린다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;시동감도 상한은 500 [Ω]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="AH64" s="32" t="inlineStr">
         <is>
-          <t>① 아크가 끊긴 뒤 낮추는 값은 10 [V] 가 아니라 25 [V] 이하다.&lt;br&gt;② 용접 시에는 무부하전압을 부하전압으로 바꾸는 것이지 그 반대가 아니다.&lt;br&gt;④ SCR 을 쓴 것은 무접점방식이다.</t>
+          <t>① 아크가 끊긴 뒤 낮추는 값은 10 [V]가 아니라 25 [V] 이하다.&lt;br&gt;② 용접 시에는 무부하전압을 부하전압으로 바꾸는 것이지 그 반대가 아니다.&lt;br&gt;④ SCR을 쓴 것은 무접점방식이다.</t>
         </is>
       </c>
       <c r="AI64" s="32" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="AG65" s="32" t="inlineStr">
         <is>
-          <t>주파수가 높을수록 &lt;strong&gt;최소감지전류는 커진다&lt;/strong&gt; — &lt;strong&gt;고주파일수록 덜 위험&lt;/strong&gt; 하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;전격의 위험을 좌우하는 것&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;요인&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;통전전류의 크기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1차적 요인&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 크게 좌우한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;통전시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;길수록 위험&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;통전경로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;심장을 지날수록 위험&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;왼손-가슴이 가장 위험&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전원의 종류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;교류가 직류보다 위험&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;극성이 바뀌어 근육이 경련&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주파수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높을수록 덜 위험&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최소감지전류가 커진다&lt;/u&gt; · 상용 60 [Hz] 가 가장 위험&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>주파수가 높을수록 &lt;strong&gt;최소감지전류는 커진다&lt;/strong&gt; — &lt;strong&gt;고주파일수록 덜 위험&lt;/strong&gt;하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;전격의 위험을 좌우하는 것&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;요인&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;통전전류의 크기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1차적 요인&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 크게 좌우한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;통전시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;길수록 위험&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;통전경로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;심장을 지날수록 위험&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;왼손-가슴이 가장 위험&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전원의 종류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;교류가 직류보다 위험&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;극성이 바뀌어 근육이 경련&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주파수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높을수록 덜 위험&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최소감지전류가 커진다&lt;/u&gt; · 상용 60 [Hz]가 가장 위험&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH65" s="32" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="AG66" s="32" t="inlineStr">
         <is>
-          <t>접지는 &lt;strong&gt;대지전위 상승을 억제&lt;/strong&gt; 하고 &lt;strong&gt;절연강도를 낮출 수 있게&lt;/strong&gt; 해 준다. &lt;strong&gt;「상승유도」와 「증가」로 뒤집어&lt;/strong&gt; 놓았다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;접지의 목적&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;목적&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;누설전류로 인한 감전 방지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;낙뢰로 인한 피해 방지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지락사고 시 대지전위 상승 억제와 절연강도 경감&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「상승유도·증가」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지락사고 시 보호계전기의 신속한 동작&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정전기 축적 방지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기기의 오동작 방지(노이즈 대책)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>접지는 &lt;strong&gt;대지전위 상승을 억제&lt;/strong&gt;하고 &lt;strong&gt;절연강도를 낮출 수 있게&lt;/strong&gt; 해 준다. &lt;strong&gt;「상승유도」와 「증가」로 뒤집어&lt;/strong&gt; 놓았다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;접지의 목적&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;목적&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;누설전류로 인한 감전 방지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;낙뢰로 인한 피해 방지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지락사고 시 대지전위 상승 억제와 절연강도 경감&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「상승유도·증가」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지락사고 시 보호계전기의 신속한 동작&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정전기 축적 방지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기기의 오동작 방지(노이즈 대책)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH66" s="32" t="inlineStr">
@@ -9646,7 +9646,7 @@
         <v>1</v>
       </c>
       <c r="Q67" s="32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R67" s="32" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
       <c r="S67" s="32" t="inlineStr"/>
       <c r="T67" s="32" t="inlineStr">
         <is>
-          <t>원본 시행일 2014.03.02 (1회 출제) | 자동판정 빈출도1 · 개념형 · 난이도1</t>
+          <t>원본 시행일 2014.03.02 (1회 출제) | 자동판정 빈출도1 · 개념형 · 난이도2</t>
         </is>
       </c>
       <c r="U67" s="32" t="inlineStr">
@@ -9664,7 +9664,11 @@
           <t>다음 보기의 누전차단기에서 정격감도전류에서 동작시간이 짧은 두 종류를 알맞게 고른 것은?</t>
         </is>
       </c>
-      <c r="V67" s="32" t="inlineStr"/>
+      <c r="V67" s="32" t="inlineStr">
+        <is>
+          <t>고속형 누전차단기 · 시연형 누전차단기 · 반한시형 누전차단기 · 감전방지용 누전차단기</t>
+        </is>
+      </c>
       <c r="W67" s="32" t="inlineStr"/>
       <c r="X67" s="32" t="inlineStr">
         <is>
@@ -9824,17 +9828,17 @@
       </c>
       <c r="AG68" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정격감도전류 30 [mA] 이하, 동작시간 0.03초 이내&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;감전방지용 누전차단기&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일반 장소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [mA] 이하, 0.03초 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물기가 있는 장소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;15 [mA] 이하, 0.03초 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설치 대상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대지전압 150 [V] 를 넘는 이동형·휴대형 전기기계기구, 물 등 도전성이 높은 액체가 있는 습윤장소, 철판·철골 위 등 도전성이 높은 장소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;정격감도전류 30 [mA] 이하, 동작시간 0.03초 이내&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;감전방지용 누전차단기&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일반 장소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [mA] 이하, 0.03초 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물기가 있는 장소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;15 [mA] 이하, 0.03초 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설치 대상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대지전압 150 [V]를 넘는 이동형·휴대형 전기기계기구, 물 등 도전성이 높은 액체가 있는 습윤장소, 철판·철골 위 등 도전성이 높은 장소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH68" s="32" t="inlineStr">
         <is>
-          <t>① 10 [mA] 는 기준값이 아니다.&lt;br&gt;② 20 [mA] 와 0.01초도 아니다.&lt;br&gt;④ 50 [mA] 와 0.1초도 아니다.</t>
+          <t>① 10 [mA]는 기준값이 아니다.&lt;br&gt;② 20 [mA]와 0.01초도 아니다.&lt;br&gt;④ 50 [mA]와 0.1초도 아니다.</t>
         </is>
       </c>
       <c r="AI68" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;감전방지용 누전차단기&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;30 [mA] 는 「사람이 스스로 손을 뗄 수 있는 한계」&lt;/strong&gt; 근처이고 &lt;strong&gt;0.03초는 「심실세동에 이르기 전」&lt;/strong&gt;이다 — &lt;strong&gt;두 숫자 모두 사람의 몸에서 나온&lt;/strong&gt; 값이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;30 [mA], 0.03초&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;감전방지용 누전차단기&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;30 [mA]는 「사람이 스스로 손을 뗄 수 있는 한계」&lt;/strong&gt; 근처이고 &lt;strong&gt;0.03초는 「심실세동에 이르기 전」&lt;/strong&gt;이다 — &lt;strong&gt;두 숫자 모두 사람의 몸에서 나온&lt;/strong&gt; 값이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;30 [mA], 0.03초&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10463,7 +10467,7 @@
       </c>
       <c r="AI73" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;위험장소의 배선방법&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;폭연성 분진이 가장 엄격&lt;/strong&gt; 하다 — &lt;strong&gt;금속관과 케이블 둘뿐이고 그마저 캡타이어는 뺀다&lt;/strong&gt;. &lt;strong&gt;가연성 분진으로 내려오면 합성수지관이 더해진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;폭연성 분진은 금속관 공사&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;위험장소의 배선방법&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;폭연성 분진이 가장 엄격&lt;/strong&gt;하다 — &lt;strong&gt;금속관과 케이블 둘뿐이고 그마저 캡타이어는 뺀다&lt;/strong&gt;. &lt;strong&gt;가연성 분진으로 내려오면 합성수지관이 더해진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;폭연성 분진은 금속관 공사&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10582,17 +10586,17 @@
       </c>
       <c r="AG74" s="32" t="inlineStr">
         <is>
-          <t>$V = IR = 0.003 \times 5 {,} 000 = 15$ [V] 이므로 $Q = CV = 0.1 \times 15 = 1.5$ [μC] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;전하 · 전압 · 정전용량&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;옴의 법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V = I R$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;먼저 전압을 구한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Q = C V$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방전에너지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$W = \dfrac{1}{2} C V^{2} = \dfrac{1}{2} Q V$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단위 짝&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;[μF] × [V] = [μC]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;그대로 곱하면 된다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$V = IR = 0.003 \times 5 {,} 000 = 15$ [V]이므로 $Q = CV = 0.1 \times 15 = 1.5$ [μC]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;전하 · 전압 · 정전용량&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;옴의 법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V = I R$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;먼저 전압을 구한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Q = C V$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방전에너지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$W = \dfrac{1}{2} C V^{2} = \dfrac{1}{2} Q V$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단위 짝&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;[μF] × [V] = [μC]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;그대로 곱하면 된다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH74" s="32" t="inlineStr">
         <is>
-          <t>① 0.5 [μC] 는 계산과 맞지 않는다.&lt;br&gt;② 1.0 [μC] 도 그렇다.&lt;br&gt;④ 2.0 [μC] 도 그렇다.</t>
+          <t>① 0.5 [μC]는 계산과 맞지 않는다.&lt;br&gt;② 1.0 [μC] 도 그렇다.&lt;br&gt;④ 2.0 [μC] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI74" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;인체의 정전용량과 대전전하&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;두 단계로 나눠 풀면 단위 걱정이 없다&lt;/strong&gt; — &lt;strong&gt;먼저 &lt;/strong&gt;$V = IR$&lt;strong&gt; 로 전압, 그다음 &lt;/strong&gt;$Q = CV$. &lt;strong&gt;[μF] 와 [μC] 는 접두어가 같아 그대로 곱하면&lt;/strong&gt; 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $Q = CV$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;인체의 정전용량과 대전전하&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;두 단계로 나눠 풀면 단위 걱정이 없다&lt;/strong&gt; — &lt;strong&gt;먼저 &lt;/strong&gt;$V = IR$&lt;strong&gt;로 전압, 그다음 &lt;/strong&gt;$Q = CV$. &lt;strong&gt;[μF]와 [μC]는 접두어가 같아 그대로 곱하면&lt;/strong&gt; 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $Q = CV$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10850,7 +10854,7 @@
       </c>
       <c r="AI76" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;화약류 저장소의 전기설비&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;화약류 저장소는 전기설비를 두지 않는 것이 원칙&lt;/strong&gt;이고 조명만 예외다 — &lt;strong&gt;그래서 대지전압도 300 [V] 로 낮게&lt;/strong&gt; 묶는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;대지전압 300 [V] 이하&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;화약류 저장소의 전기설비&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;화약류 저장소는 전기설비를 두지 않는 것이 원칙&lt;/strong&gt;이고 조명만 예외다 — &lt;strong&gt;그래서 대지전압도 300 [V]로 낮게&lt;/strong&gt; 묶는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;대지전압 300 [V] 이하&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11227,7 +11231,7 @@
       </c>
       <c r="AG79" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;단락접지 상태를 수시로 확인&lt;/strong&gt; 하는 것은 &lt;strong&gt;작업 「중」&lt;/strong&gt;의 조치다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정전작업의 조치&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;때&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업 전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전로 차단 · 잠금장치와 표지판 · 검전기로 무전압 확인 · 잔류전하 방전 · 단락접지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업 중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업지휘자의 지휘 · 단락접지 상태 수시 확인 · 근접 충전부 방호 · 절연용 보호구 착용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업 후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;단락접지 제거 · 작업자 이탈 확인 · 표지판 철거 · 송전 재개&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;단락접지 상태를 수시로 확인&lt;/strong&gt;하는 것은 &lt;strong&gt;작업 「중」&lt;/strong&gt;의 조치다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정전작업의 조치&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;때&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업 전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전로 차단 · 잠금장치와 표지판 · 검전기로 무전압 확인 · 잔류전하 방전 · 단락접지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업 중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업지휘자의 지휘 · 단락접지 상태 수시 확인 · 근접 충전부 방호 · 절연용 보호구 착용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업 후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;단락접지 제거 · 작업자 이탈 확인 · 표지판 철거 · 송전 재개&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH79" s="32" t="inlineStr">
@@ -11739,7 +11743,7 @@
       </c>
       <c r="AG83" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;칼륨&lt;/strong&gt;이다. &lt;strong&gt;이온화 경향이 커서 산과 만나면 수소를 내며 격렬히 반응&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;금속의 이온화 경향&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;차례&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;K &amp;gt; Ca &amp;gt; Na &amp;gt; Mg &amp;gt; Al &amp;gt; Zn &amp;gt; Fe &amp;gt; Ni &amp;gt; Sn &amp;gt; Pb &amp;gt; (H) &amp;gt; Cu &amp;gt; Hg &amp;gt; Ag &amp;gt; Pt &amp;gt; Au&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소보다 앞&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;산과 만나 수소를 낸다&lt;/u&gt; — 칼륨 · 나트륨 · 마그네슘 · 알루미늄 · 아연 · 철&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소보다 뒤&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;산과 반응하지 않는다&lt;/u&gt; — &lt;u&gt;구리 · 수은 · 은 · 백금 · 금&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;칼륨·나트륨&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;물과도 반응해 수소를 낸다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;칼륨&lt;/strong&gt;이다. &lt;strong&gt;이온화 경향이 커서 산과 만나면 수소를 내며 격렬히 반응&lt;/strong&gt;한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;금속의 이온화 경향&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;차례&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;K &amp;gt; Ca &amp;gt; Na &amp;gt; Mg &amp;gt; Al &amp;gt; Zn &amp;gt; Fe &amp;gt; Ni &amp;gt; Sn &amp;gt; Pb &amp;gt; (H) &amp;gt; Cu &amp;gt; Hg &amp;gt; Ag &amp;gt; Pt &amp;gt; Au&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소보다 앞&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;산과 만나 수소를 낸다&lt;/u&gt; — 칼륨 · 나트륨 · 마그네슘 · 알루미늄 · 아연 · 철&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소보다 뒤&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;산과 반응하지 않는다&lt;/u&gt; — &lt;u&gt;구리 · 수은 · 은 · 백금 · 금&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;칼륨·나트륨&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;물과도 반응해 수소를 낸다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH83" s="32" t="inlineStr">
@@ -11826,7 +11830,7 @@
       </c>
       <c r="U84" s="32" t="inlineStr">
         <is>
-          <t>NH4NO3 의 가열, 분해로부터 생성되는 무색의 가스로 일명 웃음가스라고도 하는 것은?</t>
+          <t>NH4NO3의 가열, 분해로부터 생성되는 무색의 가스로 일명 웃음가스라고도 하는 것은?</t>
         </is>
       </c>
       <c r="V84" s="32" t="inlineStr"/>
@@ -11865,12 +11869,12 @@
       </c>
       <c r="AH84" s="32" t="inlineStr">
         <is>
-          <t>② NO₂ 는 적갈색의 자극성 가스다.&lt;br&gt;③ N₂O₄ 는 NO₂ 의 이량체다.&lt;br&gt;④ NO 는 무색이나 웃음가스가 아니다.</t>
+          <t>② NO₂ 는 적갈색의 자극성 가스다.&lt;br&gt;③ N₂O₄ 는 NO₂ 의 이량체다.&lt;br&gt;④ NO는 무색이나 웃음가스가 아니다.</t>
         </is>
       </c>
       <c r="AI84" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;질산암모늄의 분해&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;질산암모늄은 비료이자 폭약&lt;/strong&gt;이다 — &lt;strong&gt;가열하면 아산화질소와 물로 갈라지고, 밀폐된 채 급격히 분해하면 폭발&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;웃음가스는 N₂O&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;질산암모늄의 분해&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;질산암모늄은 비료이자 폭약&lt;/strong&gt;이다 — &lt;strong&gt;가열하면 아산화질소와 물로 갈라지고, 밀폐된 채 급격히 분해하면 폭발&lt;/strong&gt;한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;웃음가스는 N₂O&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11998,7 @@
       </c>
       <c r="AH85" s="32" t="inlineStr">
         <is>
-          <t>① 메탄은 5 ~ 15 [vol%] 다.&lt;br&gt;② 부탄은 1.8 ~ 8.4 [vol%] 다.&lt;br&gt;③ 톨루엔은 1.4 ~ 6.7 [vol%] 다.</t>
+          <t>① 메탄은 5 ~ 15 [vol%]다.&lt;br&gt;② 부탄은 1.8 ~ 8.4 [vol%]다.&lt;br&gt;③ 톨루엔은 1.4 ~ 6.7 [vol%]다.</t>
         </is>
       </c>
       <c r="AI85" s="32" t="inlineStr">
@@ -12118,17 +12122,17 @@
       </c>
       <c r="AG86" s="32" t="inlineStr">
         <is>
-          <t>$H = \dfrac{U - L}{L} = \dfrac{75 - 4}{4} = 17.75$ 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;위험도(H)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$H = \dfrac{U - L}{L}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;U 는 상한, L 은 하한&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{75 - 4}{4} = 17.75$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소의 값&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아세틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{81 - 2.5}{2.5} = 31.4$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 크다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하한이 낮고 범위가 넓을수록 크다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$H = \dfrac{U - L}{L} = \dfrac{75 - 4}{4} = 17.75$다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;위험도(H)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$H = \dfrac{U - L}{L}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;U는 상한, L은 하한&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{75 - 4}{4} = 17.75$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소의 값&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아세틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{81 - 2.5}{2.5} = 31.4$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 크다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하한이 낮고 범위가 넓을수록 크다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH86" s="32" t="inlineStr">
         <is>
-          <t>① 16.75 는 분자에서 1 을 더 뺀 값이다.&lt;br&gt;③ 18.75 는 하한을 빼지 않은 값이다.&lt;br&gt;④ 19.75 는 계산과 맞지 않는다.</t>
+          <t>① 16.75는 분자에서 1을 더 뺀 값이다.&lt;br&gt;③ 18.75는 하한을 빼지 않은 값이다.&lt;br&gt;④ 19.75는 계산과 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI86" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;위험도(H)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;분모가 하한&lt;/strong&gt;이므로 &lt;strong&gt;하한이 낮을수록 위험도가 급격히 커진다&lt;/strong&gt;. &lt;strong&gt;「−L 을 빠뜨려 75/4 = 18.75」&lt;/strong&gt;로 가기 쉽다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $H = ( U - L ) / L$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;위험도(H)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;분모가 하한&lt;/strong&gt;이므로 &lt;strong&gt;하한이 낮을수록 위험도가 급격히 커진다&lt;/strong&gt;. &lt;strong&gt;「−L을 빠뜨려 75/4 = 18.75」&lt;/strong&gt;로 가기 쉽다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $H = ( U - L ) / L$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12247,7 +12251,7 @@
       </c>
       <c r="AG87" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;질소 100%&lt;/strong&gt;다. &lt;strong&gt;IG 는 Inert Gas, 뒤의 세 자리는 질소·아르곤·이산화탄소의 비율&lt;/strong&gt;을 나타낸다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;불활성기체 소화약제&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;약제&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구성&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;IG-01&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아르곤 100%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;IG-100&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;질소 100%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;IG-55&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;질소 50% + 아르곤 50%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;IG-541&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;질소 52% + 아르곤 40% + 이산화탄소 8%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;읽는 법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;세 자리는 차례로 N₂ · Ar · CO₂ 의 십의 자리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;질소 100%&lt;/strong&gt;다. &lt;strong&gt;IG는 Inert Gas, 뒤의 세 자리는 질소·아르곤·이산화탄소의 비율&lt;/strong&gt;을 나타낸다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;불활성기체 소화약제&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;약제&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구성&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;IG-01&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아르곤 100%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;IG-100&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;질소 100%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;IG-55&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;질소 50% + 아르곤 50%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;IG-541&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;질소 52% + 아르곤 40% + 이산화탄소 8%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;읽는 법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;세 자리는 차례로 N₂ · Ar · CO₂ 의 십의 자리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH87" s="32" t="inlineStr">
@@ -12257,7 +12261,7 @@
       </c>
       <c r="AI87" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;불활성기체 소화약제&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;번호의 세 자리가 곧 조성&lt;/strong&gt;이다 — &lt;strong&gt;IG-541 은 5 · 4 · 1 곧 질소 52 · 아르곤 40 · 이산화탄소 8&lt;/strong&gt;. &lt;strong&gt;IG-100 은 1 · 0 · 0 이므로 질소뿐&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;IG-100 은 질소&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;불활성기체 소화약제&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;번호의 세 자리가 곧 조성&lt;/strong&gt;이다 — &lt;strong&gt;IG-541은 5 · 4 · 1 곧 질소 52 · 아르곤 40 · 이산화탄소 8&lt;/strong&gt;. &lt;strong&gt;IG-100은 1 · 0 · 0이므로 질소뿐&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;IG-100은 질소&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12376,12 +12380,12 @@
       </c>
       <c r="AG88" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;약 1,100&lt;/strong&gt;으로 거의 일정하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;버제스-휠러(Burgess-Wheeler) 법칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$L \times Q \fallingdotseq 1 {,} 100$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;L 은 폭발하한계 [vol%], Q 는 연소열 [kcal/mol]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연소열이 큰 물질일수록 하한이 낮다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;쓰임&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연소열만 알면 폭발하한계를 어림할 수 있다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;약 1,100&lt;/strong&gt;으로 거의 일정하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;버제스-휠러(Burgess-Wheeler) 법칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$L \times Q \fallingdotseq 1 {,} 100$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;L은 폭발하한계 [vol%], Q는 연소열 [kcal/mol]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연소열이 큰 물질일수록 하한이 낮다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;쓰임&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연소열만 알면 폭발하한계를 어림할 수 있다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH88" s="32" t="inlineStr">
         <is>
-          <t>② 2,800 은 이 법칙의 값이 아니다.&lt;br&gt;③ 3,200 도 그렇다.&lt;br&gt;④ 3,800 도 그렇다.</t>
+          <t>② 2,800은 이 법칙의 값이 아니다.&lt;br&gt;③ 3,200 도 그렇다.&lt;br&gt;④ 3,800 도 그렇다.</t>
         </is>
       </c>
       <c r="AI88" s="32" t="inlineStr">
@@ -12505,7 +12509,7 @@
       </c>
       <c r="AG89" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;예열법&lt;/strong&gt;이다. &lt;strong&gt;용기를 미리 데워 두고 시료를 넣어 불붙는 온도를 잰다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;자연발화점(AIT)의 측정&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기체·증기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;예열법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;미리 데운 용기에 시료를 넣는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고체(분진)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가열판법 · 용기법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;영향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;압력이 높을수록, 산소농도가 높을수록, 용기가 클수록 AIT 가 낮아진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;점화원 없이 스스로 불붙는 최저 온도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;예열법&lt;/strong&gt;이다. &lt;strong&gt;용기를 미리 데워 두고 시료를 넣어 불붙는 온도를 잰다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;자연발화점(AIT)의 측정&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기체·증기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;예열법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;미리 데운 용기에 시료를 넣는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고체(분진)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가열판법 · 용기법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;영향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;압력이 높을수록, 산소농도가 높을수록, 용기가 클수록 AIT가 낮아진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;점화원 없이 스스로 불붙는 최저 온도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH89" s="32" t="inlineStr">
@@ -12515,7 +12519,7 @@
       </c>
       <c r="AI89" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;자연발화점의 측정&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「예열」이라는 낱말이 곧 방법&lt;/strong&gt;이다 — &lt;strong&gt;그릇을 먼저 달구고 시료를 떨어뜨려 스스로 불붙는지&lt;/strong&gt; 본다. &lt;strong&gt;나머지 셋은 없는 이름&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;기체의 AIT 는 예열법&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;자연발화점의 측정&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「예열」이라는 낱말이 곧 방법&lt;/strong&gt;이다 — &lt;strong&gt;그릇을 먼저 달구고 시료를 떨어뜨려 스스로 불붙는지&lt;/strong&gt; 본다. &lt;strong&gt;나머지 셋은 없는 이름&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;기체의 AIT는 예열법&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12642,17 @@
       </c>
       <c r="AG90" s="32" t="inlineStr">
         <is>
-          <t>가연성분만 다시 나누면 헥산 25%, 메탄 62.5%, 에틸렌 12.5% 다. $\dfrac{100}{L} = \dfrac{25}{1.1} + \dfrac{62.5}{5.0} + \dfrac{12.5}{2.7} = 39.86$ 이므로 $L \fallingdotseq 2.51$ [vol%] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;르 샤틀리에 식으로 푸는 차례&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;차례&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;공기를 빼고 가연성분만 100% 로 다시 나눈다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 2.5 : 0.5 → 25 : 62.5 : 12.5&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;25/1.1 + 62.5/5.0 + 12.5/2.7 = 39.86&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;L = 100 ÷ 39.86 = 2.51 [vol%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>가연성분만 다시 나누면 헥산 25%, 메탄 62.5%, 에틸렌 12.5%다. $\dfrac{100}{L} = \dfrac{25}{1.1} + \dfrac{62.5}{5.0} + \dfrac{12.5}{2.7} = 39.86$이므로 $L \fallingdotseq 2.51$ [vol%]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;르 샤틀리에 식으로 푸는 차례&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;차례&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;공기를 빼고 가연성분만 100%로 다시 나눈다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 2.5 : 0.5 → 25 : 62.5 : 12.5&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;25/1.1 + 62.5/5.0 + 12.5/2.7 = 39.86&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;L = 100 ÷ 39.86 = 2.51 [vol%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH90" s="32" t="inlineStr">
         <is>
-          <t>② 7.51 [vol%] 는 계산과 맞지 않는다.&lt;br&gt;③ 12.07 [vol%] 도 그렇다.&lt;br&gt;④ 15.01 [vol%] 도 그렇다.</t>
+          <t>② 7.51 [vol%]는 계산과 맞지 않는다.&lt;br&gt;③ 12.07 [vol%] 도 그렇다.&lt;br&gt;④ 15.01 [vol%] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI90" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;르 샤틀리에 식&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;공기 96% 를 그대로 넣으면 답이 크게 어긋난다&lt;/strong&gt; — &lt;strong&gt;가연성분만 100 이 되게 다시 나누는 것&lt;/strong&gt;이 첫걸음이다. &lt;strong&gt;하한이 가장 낮은 헥산이 결과를 끌어내린다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;공기를 빼고 다시 나눈다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;르 샤틀리에 식&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;공기 96%를 그대로 넣으면 답이 크게 어긋난다&lt;/strong&gt; — &lt;strong&gt;가연성분만 100이 되게 다시 나누는 것&lt;/strong&gt;이 첫걸음이다. &lt;strong&gt;하한이 가장 낮은 헥산이 결과를 끌어내린다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;공기를 빼고 다시 나눈다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12896,7 +12900,7 @@
       </c>
       <c r="AG92" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;수산화칼륨&lt;/strong&gt;이다. &lt;strong&gt;염기류는 농도 40% 이상&lt;/strong&gt; 이라야 부식성 물질로 본다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;부식성 물질의 농도 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;농도&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부식성 산류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;염산 · 황산 · 질산&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20% 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인산 · 아세트산 · 불산&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;60% 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부식성 염기류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수산화나트륨 · 수산화칼륨&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40% 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;수산화칼륨&lt;/strong&gt;이다. &lt;strong&gt;염기류는 농도 40% 이상&lt;/strong&gt;이라야 부식성 물질로 본다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;부식성 물질의 농도 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;농도&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부식성 산류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;염산 · 황산 · 질산&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20% 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인산 · 아세트산 · 불산&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;60% 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부식성 염기류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수산화나트륨 · 수산화칼륨&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40% 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH92" s="32" t="inlineStr">
@@ -13030,7 +13034,7 @@
       </c>
       <c r="AH93" s="32" t="inlineStr">
         <is>
-          <t>② 암모니아는 25 [ppm] 으로 넷 가운데 가장 높다.&lt;br&gt;③ 니트로벤젠은 1 [ppm] 이다.&lt;br&gt;④ 황화수소는 10 [ppm] 이다.</t>
+          <t>② 암모니아는 25 [ppm]으로 넷 가운데 가장 높다.&lt;br&gt;③ 니트로벤젠은 1 [ppm]이다.&lt;br&gt;④ 황화수소는 10 [ppm]이다.</t>
         </is>
       </c>
       <c r="AI93" s="32" t="inlineStr">
@@ -13154,17 +13158,17 @@
       </c>
       <c r="AG94" s="32" t="inlineStr">
         <is>
-          <t>$EI = \dfrac{20}{25} + \dfrac{20}{50} = 0.8 + 0.4 = 1.2$ 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;혼합물질의 노출지수(EI)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;노출지수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$EI = \sum \dfrac{C_{i}}{T_{i}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C 는 실제 농도, T 는 노출기준&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;EI ≤ 1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기준 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;EI &amp;gt; 1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기준을 넘었다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항은 1.2 로 초과&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전제&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상가작용(같은 부위에 작용)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다른 부위면 각각 따로 본다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$EI = \dfrac{20}{25} + \dfrac{20}{50} = 0.8 + 0.4 = 1.2$다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;혼합물질의 노출지수(EI)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;노출지수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$EI = \sum \dfrac{C_{i}}{T_{i}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C는 실제 농도, T는 노출기준&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;EI ≤ 1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기준 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;EI &amp;gt; 1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기준을 넘었다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항은 1.2로 초과&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전제&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상가작용(같은 부위에 작용)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다른 부위면 각각 따로 본다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH94" s="32" t="inlineStr">
         <is>
-          <t>① 1.0 은 계산과 맞지 않는다.&lt;br&gt;③ 1.5 도 그렇다.&lt;br&gt;④ 1.6 은 두 비를 곱한 값에 가깝다.</t>
+          <t>① 1.0은 계산과 맞지 않는다.&lt;br&gt;③ 1.5 도 그렇다.&lt;br&gt;④ 1.6은 두 비를 곱한 값에 가깝다.</t>
         </is>
       </c>
       <c r="AI94" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;혼합물질의 노출기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;각각은 기준 안이지만 더하면 넘는다&lt;/strong&gt; — &lt;strong&gt;0.8 도 0.4 도 1 보다 작지만 합이 1.2&lt;/strong&gt;다. &lt;strong&gt;이것이 상가작용을 따지는 까닭&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $EI = \sum C_{i} / T_{i}$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;혼합물질의 노출기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;각각은 기준 안이지만 더하면 넘는다&lt;/strong&gt; — &lt;strong&gt;0.8 도 0.4 도 1보다 작지만 합이 1.2&lt;/strong&gt;다. &lt;strong&gt;이것이 상가작용을 따지는 까닭&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $EI = \sum C_{i} / T_{i}$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13422,7 +13426,7 @@
       </c>
       <c r="AI96" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;분말소화약제&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;제3종만 A급(일반화재)에도 쓸 수 있다&lt;/strong&gt; — &lt;strong&gt;메타인산이 타는 물체 겉에 유리막을 만들어 다시 불붙지 못하게(방진)&lt;/strong&gt; 하기 때문이다. &lt;strong&gt;그래서 「ABC 분말」&lt;/strong&gt;이라 부른다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;메타인산은 제3종&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;분말소화약제&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;제3종만 A급(일반화재)에도 쓸 수 있다&lt;/strong&gt; — &lt;strong&gt;메타인산이 타는 물체 겉에 유리막을 만들어 다시 불붙지 못하게(방진)&lt;/strong&gt;하기 때문이다. &lt;strong&gt;그래서 「ABC 분말」&lt;/strong&gt;이라 부른다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;메타인산은 제3종&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13675,12 +13679,12 @@
       </c>
       <c r="AH98" s="32" t="inlineStr">
         <is>
-          <t>② 4 [m/s] 는 기준을 넘는다.&lt;br&gt;③ 8 [m/s] 도 그렇다.&lt;br&gt;④ 10 [m/s] 도 그렇다.</t>
+          <t>② 4 [m/s]는 기준을 넘는다.&lt;br&gt;③ 8 [m/s] 도 그렇다.&lt;br&gt;④ 10 [m/s] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI98" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;위험물 주입 시의 정전기&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;가솔린이 남은 탱크에 등유를 부으면 「불붙을 증기」와 「전하를 쌓는 액체」가 한자리에&lt;/strong&gt; 모인다 — &lt;strong&gt;속도를 1 [m/s] 로 묶는 것&lt;/strong&gt;이 그 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;주입속도 1 [m/s] 이하&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;위험물 주입 시의 정전기&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;가솔린이 남은 탱크에 등유를 부으면 「불붙을 증기」와 「전하를 쌓는 액체」가 한자리에&lt;/strong&gt; 모인다 — &lt;strong&gt;속도를 1 [m/s]로 묶는 것&lt;/strong&gt;이 그 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;주입속도 1 [m/s] 이하&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13799,7 +13803,7 @@
       </c>
       <c r="AG99" s="32" t="inlineStr">
         <is>
-          <t>불활성가스는 &lt;strong&gt;제거가 아니라 주입&lt;/strong&gt; 해야 한다. &lt;strong&gt;반응을 눌러 주는&lt;/strong&gt; 구실을 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;반응폭주를 막는 긴급차단장치&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원재료의 공급차단장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;연료를 끊는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보유 내용물의 방출장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안에 있는 것을 빼낸다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;불활성가스의 주입장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「제거」가 아니다&lt;/u&gt; — 넣어서 반응을 누른다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반응정지제 등의 공급장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;반응을 멈추는 약제&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;냉각수 등의 공급장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;열을 뺀다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>불활성가스는 &lt;strong&gt;제거가 아니라 주입&lt;/strong&gt;해야 한다. &lt;strong&gt;반응을 눌러 주는&lt;/strong&gt; 구실을 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;반응폭주를 막는 긴급차단장치&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원재료의 공급차단장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;연료를 끊는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보유 내용물의 방출장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안에 있는 것을 빼낸다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;불활성가스의 주입장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「제거」가 아니다&lt;/u&gt; — 넣어서 반응을 누른다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반응정지제 등의 공급장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;반응을 멈추는 약제&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;냉각수 등의 공급장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;열을 뺀다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH99" s="32" t="inlineStr">
@@ -14170,7 +14174,7 @@
       </c>
       <c r="AG102" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;개구부를 제한&lt;/strong&gt; 한다. &lt;strong&gt;공기가 덜 들어오면 불이 한꺼번에 번지는 시점이 늦춰진다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;플래시오버(flash over)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무엇&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;실내의 가연물이 한꺼번에 발화해 불길이 방 전체를 덮는 현상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;언제&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;화재 성장기의 끝, 최성기로 넘어가는 목&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;빨라지는 조건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개구부가 클수록 · 가연성 내장재일수록 · 실내가 뜨거울수록 · 천장이 낮을수록&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지연대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개구부 제한 · 난연 내장재 · 천장을 높게 · 가연물 줄이기&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;백드래프트와 다른 점&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;플래시오버는 산소가 있을 때, 백드래프트는 산소가 모자란 곳에 갑자기 공기가 들어올 때&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;개구부를 제한&lt;/strong&gt;한다. &lt;strong&gt;공기가 덜 들어오면 불이 한꺼번에 번지는 시점이 늦춰진다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;플래시오버(flash over)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무엇&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;실내의 가연물이 한꺼번에 발화해 불길이 방 전체를 덮는 현상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;언제&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;화재 성장기의 끝, 최성기로 넘어가는 목&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;빨라지는 조건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개구부가 클수록 · 가연성 내장재일수록 · 실내가 뜨거울수록 · 천장이 낮을수록&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지연대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개구부 제한 · 난연 내장재 · 천장을 높게 · 가연물 줄이기&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;백드래프트와 다른 점&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;플래시오버는 산소가 있을 때, 백드래프트는 산소가 모자란 곳에 갑자기 공기가 들어올 때&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH102" s="32" t="inlineStr">
@@ -14299,7 +14303,7 @@
       </c>
       <c r="AG103" s="32" t="inlineStr">
         <is>
-          <t>진동기를 많이 쓸수록 &lt;strong&gt;측압이 커져 위험&lt;/strong&gt; 하다. &lt;strong&gt;다지는 데는 좋지만 거푸집에는 부담&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;콘크리트 타설작업의 유의사항&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;치는 도중 지보공·거푸집의 이상 유무를 확인한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높은 곳에서는 호퍼로 받아 슈트로 부어 넣는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한 곳에 치우쳐 붓지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;편심하중을 피한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;진동기는 필요한 만큼만 쓴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;많이 쓸수록 측압이 커진다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;타설속도는 천천히&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>진동기를 많이 쓸수록 &lt;strong&gt;측압이 커져 위험&lt;/strong&gt;하다. &lt;strong&gt;다지는 데는 좋지만 거푸집에는 부담&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;콘크리트 타설작업의 유의사항&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;치는 도중 지보공·거푸집의 이상 유무를 확인한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높은 곳에서는 호퍼로 받아 슈트로 부어 넣는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한 곳에 치우쳐 붓지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;편심하중을 피한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;진동기는 필요한 만큼만 쓴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;많이 쓸수록 측압이 커진다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;타설속도는 천천히&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH103" s="32" t="inlineStr">
@@ -14432,7 +14436,7 @@
       </c>
       <c r="AG104" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;1.5 [m] 이상 1.8 [m] 이하&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;강관비계의 구조&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥의 간격 — 띠장 방향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.85 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;옛 기준 1.5 ~ 1.8 [m]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥의 간격 — 장선 방향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.5 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;띠장 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.0 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥의 최고부에서 31 [m] 되는 지점 아래&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2개의 강관으로 묶어 세울 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;적재하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;비계기둥 사이 400 [kg] 을 넘지 않을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;1.5 [m] 이상 1.8 [m] 이하&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;강관비계의 구조&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥의 간격 — 띠장 방향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.85 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;옛 기준 1.5 ~ 1.8 [m]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥의 간격 — 장선 방향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.5 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;띠장 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.0 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥의 최고부에서 31 [m] 되는 지점 아래&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2개의 강관으로 묶어 세울 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;적재하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;비계기둥 사이 400 [kg]을 넘지 않을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH104" s="32" t="inlineStr">
@@ -14561,17 +14565,17 @@
       </c>
       <c r="AG105" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;10 [m] 를 넘지 않게&lt;/strong&gt; 한다. &lt;strong&gt;떨어지는 높이가 클수록 충격이 커지기&lt;/strong&gt; 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;추락방호망의 설치기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업면에서 망까지 수직거리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [m] 를 넘지 않을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내민 길이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;벽면에서 3 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;바깥쪽 끝이 벽면에서&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;처짐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;짧은 변 길이의 12% 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;겹침&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이어 쓸 때는 60 [cm] 이상 겹치거나 묶을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방망 아래 여유&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바닥면에서 충분한 높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;10 [m]를 넘지 않게&lt;/strong&gt; 한다. &lt;strong&gt;떨어지는 높이가 클수록 충격이 커지기&lt;/strong&gt; 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;추락방호망의 설치기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업면에서 망까지 수직거리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [m]를 넘지 않을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내민 길이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;벽면에서 3 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;바깥쪽 끝이 벽면에서&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;처짐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;짧은 변 길이의 12% 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;겹침&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이어 쓸 때는 60 [cm] 이상 겹치거나 묶을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방망 아래 여유&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바닥면에서 충분한 높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH105" s="32" t="inlineStr">
         <is>
-          <t>① 5 [m] 는 기준값이 아니다.&lt;br&gt;③ 15 [m] 도 그렇다.&lt;br&gt;④ 17 [m] 도 그렇다.</t>
+          <t>① 5 [m]는 기준값이 아니다.&lt;br&gt;③ 15 [m] 도 그렇다.&lt;br&gt;④ 17 [m] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI105" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;추락방호망&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;숫자가 「10 · 3 · 12% · 60」&lt;/strong&gt;이다. &lt;strong&gt;10 [m] 라는 값이 「이 정도 높이에서 떨어져도 방망이 받아 낼 수 있다」&lt;/strong&gt;는 한계다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;수직거리 10 [m] 이하&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 추락방호망 규정은 &lt;u&gt;2021.5.28 개정&lt;/u&gt;으로 안전보건기준규칙 &lt;u&gt;제42조&lt;/u&gt;로 옮겨 실렸다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;추락방호망&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;숫자가 「10 · 3 · 12% · 60」&lt;/strong&gt;이다. &lt;strong&gt;10 [m]라는 값이 「이 정도 높이에서 떨어져도 방망이 받아 낼 수 있다」&lt;/strong&gt;는 한계다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;수직거리 10 [m] 이하&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 추락방호망 규정은 &lt;u&gt;2021.5.28 개정&lt;/u&gt;으로 안전보건기준규칙 &lt;u&gt;제42조&lt;/u&gt;로 옮겨 실렸다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14957,12 @@
       </c>
       <c r="AH108" s="32" t="inlineStr">
         <is>
-          <t>① 1 : 0.3 은 기준에 없는 값이다.&lt;br&gt;② 1 : 0.5 는 경암의 기울기다.&lt;br&gt;③ 1 : 0.8 도 기준에 없는 값이다.</t>
+          <t>① 1 : 0.3은 기준에 없는 값이다.&lt;br&gt;② 1 : 0.5는 경암의 기울기다.&lt;br&gt;③ 1 : 0.8 도 기준에 없는 값이다.</t>
         </is>
       </c>
       <c r="AI108" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;굴착면의 기울기&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;단단할수록 세우고 무를수록 눕힌다&lt;/strong&gt; — &lt;strong&gt;경암 0.5 → 연암·풍화암 1.0 → 그 밖의 흙 1.2 → 모래 1.8&lt;/strong&gt;로 커진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;연암은 1 : 1.0&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;2021.11.19 개정&lt;/u&gt;으로 &lt;u&gt;풍화암과 연암이 1 : 1.0 으로 통합&lt;/u&gt; 되고 &lt;u&gt;「보통흙」이 「그 밖의 흙 1 : 1.2」로 정리&lt;/u&gt; 하였다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;굴착면의 기울기&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;단단할수록 세우고 무를수록 눕힌다&lt;/strong&gt; — &lt;strong&gt;경암 0.5 → 연암·풍화암 1.0 → 그 밖의 흙 1.2 → 모래 1.8&lt;/strong&gt;로 커진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;연암은 1 : 1.0&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;2021.11.19 개정&lt;/u&gt;으로 &lt;u&gt;풍화암과 연암이 1 : 1.0으로 통합&lt;/u&gt;되고 &lt;u&gt;「보통흙」이 「그 밖의 흙 1 : 1.2」로 정리&lt;/u&gt; 하였다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15597,7 +15601,7 @@
       </c>
       <c r="AG113" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;매월 작성하고 공사 종료 후 1년간 보존&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;산업안전보건관리비의 사용&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사용명세서 작성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;매월&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보존&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;건설공사 종료 후 1년간&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계상 대상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;총공사금액 2천만 원 이상인 건설공사&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;쓸 수 없는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;공사 수행에 필요한 시설·장비, 근로자 재해예방 외의 목적&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;매월 작성하고 공사 종료 후 1년간 보존&lt;/strong&gt;한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;산업안전보건관리비의 사용&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사용명세서 작성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;매월&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보존&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;건설공사 종료 후 1년간&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계상 대상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;총공사금액 2천만 원 이상인 건설공사&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;쓸 수 없는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;공사 수행에 필요한 시설·장비, 근로자 재해예방 외의 목적&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH113" s="32" t="inlineStr">
@@ -15984,17 +15988,17 @@
       </c>
       <c r="AG116" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;풍속 초당 10 [m] 이상&lt;/strong&gt;이면 멈춘다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;철골작업의 중지기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;풍속&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;초당 10 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강우량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시간당 1 [mm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;[cm] 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강설량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시간당 1 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「분당」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기온&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;중지기준에 없다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;풍속 초당 10 [m] 이상&lt;/strong&gt;이면 멈춘다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;철골작업의 중지기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;풍속&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;초당 10 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강우량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시간당 1 [mm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;[cm]가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강설량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시간당 1 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「분당」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기온&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;중지기준에 없다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH116" s="32" t="inlineStr">
         <is>
-          <t>① 강설량은 분당이 아니라 시간당 1 [cm] 이상이다.&lt;br&gt;② 강우량은 시간당 1 [cm] 가 아니라 1 [mm] 이상이다.&lt;br&gt;④ 기온은 철골작업 중지기준에 들지 않는다.</t>
+          <t>① 강설량은 분당이 아니라 시간당 1 [cm] 이상이다.&lt;br&gt;② 강우량은 시간당 1 [cm]가 아니라 1 [mm] 이상이다.&lt;br&gt;④ 기온은 철골작업 중지기준에 들지 않는다.</t>
         </is>
       </c>
       <c r="AI116" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;철골작업의 악천후 중지기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「10 · 1 [mm] · 1 [cm]」&lt;/strong&gt; 셋이다 — &lt;strong&gt;비는 [mm], 눈은 [cm]&lt;/strong&gt;로 단위가 다르다는 점이 갈림길이다. &lt;strong&gt;타워크레인 운전중지 15 [m/s] 와 헷갈리지 않게&lt;/strong&gt; 갈라 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;풍속 10 [m/s], 비 1 [mm], 눈 1 [cm]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;철골작업의 악천후 중지기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「10 · 1 [mm] · 1 [cm]」&lt;/strong&gt; 셋이다 — &lt;strong&gt;비는 [mm], 눈은 [cm]&lt;/strong&gt;로 단위가 다르다는 점이 갈림길이다. &lt;strong&gt;타워크레인 운전중지 15 [m/s]와 헷갈리지 않게&lt;/strong&gt; 갈라 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;풍속 10 [m/s], 비 1 [mm], 눈 1 [cm]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16113,7 +16117,7 @@
       </c>
       <c r="AG117" s="32" t="inlineStr">
         <is>
-          <t>높이 기준은 &lt;strong&gt;20 [m] 이상&lt;/strong&gt;이다. &lt;strong&gt;15 [m] 는 들지 않는다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;외압에 대한 내력을 확인해야 하는 철골구조물&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 20 [m] 이상인 구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「15 [m]」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;구조물의 폭과 높이의 비가 1 : 4 이상인 구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이 문항의 1 : 5 는 해당한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단면구조에 현저한 차이가 있는 구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연면적당 철골량이 50 [kg/m²] 이하인 구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기둥이 타이플레이트형인 구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이음부가 현장용접인 구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>높이 기준은 &lt;strong&gt;20 [m] 이상&lt;/strong&gt;이다. &lt;strong&gt;15 [m]는 들지 않는다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;외압에 대한 내력을 확인해야 하는 철골구조물&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 20 [m] 이상인 구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「15 [m]」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;구조물의 폭과 높이의 비가 1 : 4 이상인 구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이 문항의 1 : 5는 해당한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단면구조에 현저한 차이가 있는 구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연면적당 철골량이 50 [kg/m²] 이하인 구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기둥이 타이플레이트형인 구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이음부가 현장용접인 구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH117" s="32" t="inlineStr">
@@ -16239,7 +16243,7 @@
       </c>
       <c r="AH118" s="32" t="inlineStr">
         <is>
-          <t>① 20% 는 아직 정상 범위다.&lt;br&gt;③ 15% 는 이미 위험한 상태다.&lt;br&gt;④ 10% 는 의식을 잃는 농도다.</t>
+          <t>① 20%는 아직 정상 범위다.&lt;br&gt;③ 15%는 이미 위험한 상태다.&lt;br&gt;④ 10%는 의식을 잃는 농도다.</t>
         </is>
       </c>
       <c r="AI118" s="32" t="inlineStr">
@@ -16336,7 +16340,7 @@
       <c r="W119" s="32" t="inlineStr"/>
       <c r="X119" s="32" t="inlineStr">
         <is>
-          <t>진동수의 범위는 1 ~ 90Hz 이다.</t>
+          <t>진동수의 범위는 1 ~ 90Hz이다.</t>
         </is>
       </c>
       <c r="Y119" s="32" t="inlineStr"/>
@@ -16496,12 +16500,12 @@
       </c>
       <c r="AG120" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;20 [cm] 이상&lt;/strong&gt;이다. &lt;strong&gt;보통 작업발판의 40 [cm] 보다 좁게 잡아 준&lt;/strong&gt; 예외다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;비계 조립·해체·변경 작업의 준수사항&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관리감독자의 지휘에 따를 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;조립·해체 시기와 범위, 절차를 근로자에게 알릴 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업구역에 관계 근로자가 아닌 사람의 출입을 금지하고 표지를 붙일 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비·눈 등으로 위험이 예상되면 작업을 중지할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계재료의 연결·해체작업에는 폭 20 [cm] 이상의 발판&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보통 작업발판은 40 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;재료·기구는 달줄이나 달포대로 오르내릴 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;20 [cm] 이상&lt;/strong&gt;이다. &lt;strong&gt;보통 작업발판의 40 [cm]보다 좁게 잡아 준&lt;/strong&gt; 예외다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;비계 조립·해체·변경 작업의 준수사항&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관리감독자의 지휘에 따를 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;조립·해체 시기와 범위, 절차를 근로자에게 알릴 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업구역에 관계 근로자가 아닌 사람의 출입을 금지하고 표지를 붙일 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비·눈 등으로 위험이 예상되면 작업을 중지할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계재료의 연결·해체작업에는 폭 20 [cm] 이상의 발판&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보통 작업발판은 40 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;재료·기구는 달줄이나 달포대로 오르내릴 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH120" s="32" t="inlineStr">
         <is>
-          <t>① 15 [cm] 는 기준에 못 미친다.&lt;br&gt;③ 25 [cm] 는 기준보다 넓다.&lt;br&gt;④ 30 [cm] 도 그렇다.</t>
+          <t>① 15 [cm]는 기준에 못 미친다.&lt;br&gt;③ 25 [cm]는 기준보다 넓다.&lt;br&gt;④ 30 [cm] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI120" s="32" t="inlineStr">
@@ -16625,17 +16629,17 @@
       </c>
       <c r="AG121" s="32" t="inlineStr">
         <is>
-          <t>높이는 &lt;strong&gt;밑변 최소폭의 4배 이하&lt;/strong&gt;이므로 $2 \times 4 = 8$ [m] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;이동식 비계의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최대 높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;밑변 최소폭의 4배 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항 — 8 [m]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업발판의 최대 적재하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;250 [kg] 을 넘지 않을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;바퀴&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;브레이크·쐐기 등으로 고정하고 아웃트리거를 설치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;승탑&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사람이 탄 채로 이동하지 말 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전난간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업발판 위에 설치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>높이는 &lt;strong&gt;밑변 최소폭의 4배 이하&lt;/strong&gt;이므로 $2 \times 4 = 8$ [m]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;이동식 비계의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최대 높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;밑변 최소폭의 4배 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항 — 8 [m]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업발판의 최대 적재하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;250 [kg]을 넘지 않을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;바퀴&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;브레이크·쐐기 등으로 고정하고 아웃트리거를 설치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;승탑&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사람이 탄 채로 이동하지 말 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전난간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업발판 위에 설치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH121" s="32" t="inlineStr">
         <is>
-          <t>① 4 [m] 는 2배다.&lt;br&gt;③ 10 [m] 는 5배다.&lt;br&gt;④ 14 [m] 는 7배다.</t>
+          <t>① 4 [m]는 2배다.&lt;br&gt;③ 10 [m]는 5배다.&lt;br&gt;④ 14 [m]는 7배다.</t>
         </is>
       </c>
       <c r="AI121" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;이동식 비계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;밑변이 좁고 높으면 넘어진다&lt;/strong&gt; — &lt;strong&gt;4배라는 비가 그 한계&lt;/strong&gt;다. &lt;strong&gt;250 [kg] 이라는 적재하중과 함께 잡아&lt;/strong&gt; 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;높이는 밑변 최소폭의 4배 이하&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;이동식 비계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;밑변이 좁고 높으면 넘어진다&lt;/strong&gt; — &lt;strong&gt;4배라는 비가 그 한계&lt;/strong&gt;다. &lt;strong&gt;250 [kg]이라는 적재하중과 함께 잡아&lt;/strong&gt; 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;높이는 밑변 최소폭의 4배 이하&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
